--- a/data/LookupTable_example.xlsx
+++ b/data/LookupTable_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gollnickdatasolutions-my.sharepoint.com/personal/bertgollnick_gollnickdatasolutions_onmicrosoft_com/Documents/Projects/Bildungsurlaub/KIfürJobUndAlltag/Inhalte/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{F0C0DBE1-9C68-48E4-88D7-AA838F849C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5825606-1163-4D42-BC01-121D30BA7735}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{F0C0DBE1-9C68-48E4-88D7-AA838F849C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FCC2C69-1475-42BA-9084-0E93E0382196}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8D21460-674D-4725-AFD4-9402E41F0DE5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E8D21460-674D-4725-AFD4-9402E41F0DE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -89,17 +89,18 @@
     <t>Price</t>
   </si>
   <si>
-    <t>Spalte1</t>
+    <t>Preis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot;€&quot;#,##0.00_);[Red]\(&quot;€&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,13 +121,30 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF156082"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -224,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -250,9 +268,10 @@
     <xf numFmtId="8" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -525,18 +544,14 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CABCE835-193D-4897-8AEE-A1AEC384D5B1}" name="Tabelle1" displayName="Tabelle1" ref="A1:C9" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
   <autoFilter ref="A1:C9" xr:uid="{CABCE835-193D-4897-8AEE-A1AEC384D5B1}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{679D55B6-5B28-41F3-BCAA-EA8F5403CAF6}" name="Order ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{700730B0-BD22-4527-B0DB-634A9E193945}" name="Product" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{1A529857-2DDB-46E1-9C8B-D3A0310B19EB}" name="Spalte1" dataDxfId="0">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(B2, $C:$C, $D:$D, "")</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{8BCE6039-8A5B-4F1E-8196-8E2109DA08D0}" name="Preis" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Tabelle1[[#This Row],[Product]],Tabelle2[Product],Tabelle2[Price])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -544,8 +559,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F824E2A6-AFBC-46B9-8560-046C7CBC84E8}" name="Tabelle2" displayName="Tabelle2" ref="G1:H7" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
-  <autoFilter ref="G1:H7" xr:uid="{F824E2A6-AFBC-46B9-8560-046C7CBC84E8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F824E2A6-AFBC-46B9-8560-046C7CBC84E8}" name="Tabelle2" displayName="Tabelle2" ref="F1:G7" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
+  <autoFilter ref="F1:G7" xr:uid="{F824E2A6-AFBC-46B9-8560-046C7CBC84E8}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{8FDABCA5-18F2-488D-92E4-098C1B9CC4B0}" name="Product" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{95F87D6C-E58A-4E87-B0E2-08F63EA06D88}" name="Price" dataDxfId="1"/>
@@ -869,17 +884,39 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{312458B0-1EA7-4555-B972-DD8408F15E93}">
+  <we:reference id="29673e3c-d826-4f00-92ee-162334a52b1a" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="de-DE" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;ee37f366-e99d-4f91-a454-a9025c41e2c6&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D47E91AD-3D95-4292-8638-5EE4A3B2BFDE}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -889,28 +926,32 @@
       <c r="C1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="C2" s="10">
+        <f>_xlfn.XLOOKUP(Tabelle1[[#This Row],[Product]],Tabelle2[Product],Tabelle2[Price])</f>
+        <v>950</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="7">
+      <c r="G2" s="7">
         <v>950</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -918,17 +959,17 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C2:C9" ca="1" si="0">_xlfn.XLOOKUP(B3, $C:$C, $D:$D, "")</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="1" t="s">
+        <f>_xlfn.XLOOKUP(Tabelle1[[#This Row],[Product]],Tabelle2[Product],Tabelle2[Price])</f>
+        <v>600</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="7">
+      <c r="G3" s="7">
         <v>600</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -936,17 +977,17 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
+        <f>_xlfn.XLOOKUP(Tabelle1[[#This Row],[Product]],Tabelle2[Product],Tabelle2[Price])</f>
+        <v>120</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="7">
+      <c r="G4" s="7">
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -954,17 +995,17 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="s">
+        <f>_xlfn.XLOOKUP(Tabelle1[[#This Row],[Product]],Tabelle2[Product],Tabelle2[Price])</f>
+        <v>950</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="7">
+      <c r="G5" s="7">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -972,17 +1013,17 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="1" t="s">
+        <f>_xlfn.XLOOKUP(Tabelle1[[#This Row],[Product]],Tabelle2[Product],Tabelle2[Price])</f>
+        <v>250</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="7">
+      <c r="G6" s="7">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -990,17 +1031,17 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="s">
+        <f>_xlfn.XLOOKUP(Tabelle1[[#This Row],[Product]],Tabelle2[Product],Tabelle2[Price])</f>
+        <v>45</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="8">
+      <c r="G7" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1008,11 +1049,11 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(Tabelle1[[#This Row],[Product]],Tabelle2[Product],Tabelle2[Price])</f>
+        <v>600</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -1020,8 +1061,8 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <f>_xlfn.XLOOKUP(Tabelle1[[#This Row],[Product]],Tabelle2[Product],Tabelle2[Price])</f>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
